--- a/AE69-base.xlsx
+++ b/AE69-base.xlsx
@@ -14,9 +14,9 @@
     <sheet name="Без фото" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sheet1'!$A$1:$G$1392</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sheet1'!$A$1:$G$1409</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Категории'!$A$1:$C$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Без комплектующих'!$A$1:$E$752</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Без комплектующих'!$A$1:$E$754</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Без фото'!$A$1:$E$363</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -572,7 +572,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>каталог 18 · 18.09.2026 · 1391 позиций</t>
+          <t>каталог 19 · 22.09.2026 · 1408 позиций</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1029</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="6">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>640</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8">
@@ -616,7 +616,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>751  (жёлтые ячейки в столбце «Комплектующие»)</t>
+          <t>753  (жёлтые ячейки в столбце «Комплектующие»)</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       <c r="A25" s="3" t="n"/>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Код со листа «Категории» (выпадающий список в столбце G). Пустая ячейка = «Без категории» — таких сейчас 159, лучше проставить.</t>
+          <t>Код со листа «Категории» (выпадающий список в столбце G). Пустая ячейка = «Без категории» — таких сейчас 161, лучше проставить.</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1422"/>
+  <dimension ref="A1:G1439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -41920,157 +41920,549 @@
       </c>
     </row>
     <row r="1393" ht="18" customHeight="1">
-      <c r="A1393" s="15" t="n"/>
-      <c r="B1393" s="15" t="n"/>
-      <c r="C1393" s="15" t="n"/>
-      <c r="D1393" s="15" t="n"/>
-      <c r="E1393" s="15" t="n"/>
-      <c r="F1393" s="15" t="n"/>
-      <c r="G1393" s="15" t="n"/>
+      <c r="A1393" s="11" t="inlineStr">
+        <is>
+          <t>3733</t>
+        </is>
+      </c>
+      <c r="B1393" s="11" t="inlineStr">
+        <is>
+          <t>VBS 1(ГСИ 1.5)</t>
+        </is>
+      </c>
+      <c r="C1393" s="12" t="inlineStr">
+        <is>
+          <t>Клемма "трубка" соединит. с полн.изоляц.ПВХ(под пр.от 0,50 до 1,50мм кв лужён., красная) мин.100шт</t>
+        </is>
+      </c>
+      <c r="D1393" s="11" t="n"/>
+      <c r="E1393" s="13" t="n"/>
+      <c r="F1393" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ae69.ru/files/_docs/8428879.jpg,https://www.ae69.ru/files/_docs/9732895.jpg,https://www.ae69.ru/files/_docs/6244826.jpg</t>
+        </is>
+      </c>
+      <c r="G1393" s="11" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
     </row>
     <row r="1394" ht="18" customHeight="1">
-      <c r="A1394" s="15" t="n"/>
-      <c r="B1394" s="15" t="n"/>
-      <c r="C1394" s="15" t="n"/>
-      <c r="D1394" s="15" t="n"/>
-      <c r="E1394" s="15" t="n"/>
-      <c r="F1394" s="15" t="n"/>
-      <c r="G1394" s="15" t="n"/>
+      <c r="A1394" s="11" t="inlineStr">
+        <is>
+          <t>3734</t>
+        </is>
+      </c>
+      <c r="B1394" s="11" t="inlineStr">
+        <is>
+          <t>VBS 2(ГСИ 2,5)</t>
+        </is>
+      </c>
+      <c r="C1394" s="12" t="inlineStr">
+        <is>
+          <t>Клемма "трубка" соединит. с полн.изоляц.ПВХ(под пр.от 1,50 до 2,50мм кв лужён., синяя) мин.100шт</t>
+        </is>
+      </c>
+      <c r="D1394" s="11" t="n"/>
+      <c r="E1394" s="13" t="n"/>
+      <c r="F1394" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ae69.ru/files/_docs/2336086.jpg,https://www.ae69.ru/files/_docs/9488914.jpg,https://www.ae69.ru/files/_docs/8586255.jpg</t>
+        </is>
+      </c>
+      <c r="G1394" s="11" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
     </row>
     <row r="1395" ht="18" customHeight="1">
-      <c r="A1395" s="15" t="n"/>
-      <c r="B1395" s="15" t="n"/>
-      <c r="C1395" s="15" t="n"/>
-      <c r="D1395" s="15" t="n"/>
-      <c r="E1395" s="15" t="n"/>
-      <c r="F1395" s="15" t="n"/>
-      <c r="G1395" s="15" t="n"/>
+      <c r="A1395" s="11" t="inlineStr">
+        <is>
+          <t>2236</t>
+        </is>
+      </c>
+      <c r="B1395" s="11" t="inlineStr">
+        <is>
+          <t>НК2х10-1,5-01</t>
+        </is>
+      </c>
+      <c r="C1395" s="12" t="inlineStr">
+        <is>
+          <t>Набор клемм НК2 серии 1,5мм, вариант 01(DJ624-1,8A+DJ611-1,5-0,6, 2 вида по 10шт, в контейнере)</t>
+        </is>
+      </c>
+      <c r="D1395" s="11" t="n"/>
+      <c r="E1395" s="12" t="inlineStr">
+        <is>
+          <t>6785-10, 6784-10, 5991-1</t>
+        </is>
+      </c>
+      <c r="F1395" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ae69.ru/files/_docs/1897288.png,https://www.ae69.ru/files/_docs/6663982.png</t>
+        </is>
+      </c>
+      <c r="G1395" s="11" t="inlineStr">
+        <is>
+          <t>f10</t>
+        </is>
+      </c>
     </row>
     <row r="1396" ht="18" customHeight="1">
-      <c r="A1396" s="15" t="n"/>
-      <c r="B1396" s="15" t="n"/>
-      <c r="C1396" s="15" t="n"/>
-      <c r="D1396" s="15" t="n"/>
-      <c r="E1396" s="15" t="n"/>
-      <c r="F1396" s="15" t="n"/>
-      <c r="G1396" s="15" t="n"/>
+      <c r="A1396" s="11" t="inlineStr">
+        <is>
+          <t>8157</t>
+        </is>
+      </c>
+      <c r="B1396" s="11" t="inlineStr">
+        <is>
+          <t>НК2х10-2,8-01</t>
+        </is>
+      </c>
+      <c r="C1396" s="12" t="inlineStr">
+        <is>
+          <t>Набор клемм НК2 серии 2,8мм, вариант 01(8865+8891, 2 вида по 10шт, в контейнере)</t>
+        </is>
+      </c>
+      <c r="D1396" s="11" t="n"/>
+      <c r="E1396" s="12" t="inlineStr">
+        <is>
+          <t>2599-10, 2601-10, 5991-1</t>
+        </is>
+      </c>
+      <c r="F1396" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ae69.ru/files/_docs/8129921.png,https://www.ae69.ru/files/_docs/9816561.png</t>
+        </is>
+      </c>
+      <c r="G1396" s="11" t="inlineStr">
+        <is>
+          <t>f10</t>
+        </is>
+      </c>
     </row>
     <row r="1397" ht="18" customHeight="1">
-      <c r="A1397" s="15" t="n"/>
-      <c r="B1397" s="15" t="n"/>
-      <c r="C1397" s="15" t="n"/>
-      <c r="D1397" s="15" t="n"/>
-      <c r="E1397" s="15" t="n"/>
-      <c r="F1397" s="15" t="n"/>
-      <c r="G1397" s="15" t="n"/>
+      <c r="A1397" s="11" t="inlineStr">
+        <is>
+          <t>1131</t>
+        </is>
+      </c>
+      <c r="B1397" s="11" t="inlineStr">
+        <is>
+          <t>НК2х10-2,8-02</t>
+        </is>
+      </c>
+      <c r="C1397" s="12" t="inlineStr">
+        <is>
+          <t>Набор клемм НК2 серии 2,8мм, вариант 02(8865+8845, 2 вида по 10шт, в контейнере)</t>
+        </is>
+      </c>
+      <c r="D1397" s="11" t="n"/>
+      <c r="E1397" s="12" t="inlineStr">
+        <is>
+          <t>2599-10, 3140-10, 5991-1</t>
+        </is>
+      </c>
+      <c r="F1397" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ae69.ru/files/_docs/6851489.png,https://www.ae69.ru/files/_docs/2383844.png</t>
+        </is>
+      </c>
+      <c r="G1397" s="11" t="inlineStr">
+        <is>
+          <t>f10</t>
+        </is>
+      </c>
     </row>
     <row r="1398" ht="18" customHeight="1">
-      <c r="A1398" s="15" t="n"/>
-      <c r="B1398" s="15" t="n"/>
-      <c r="C1398" s="15" t="n"/>
-      <c r="D1398" s="15" t="n"/>
-      <c r="E1398" s="15" t="n"/>
-      <c r="F1398" s="15" t="n"/>
-      <c r="G1398" s="15" t="n"/>
+      <c r="A1398" s="11" t="inlineStr">
+        <is>
+          <t>2684</t>
+        </is>
+      </c>
+      <c r="B1398" s="11" t="inlineStr">
+        <is>
+          <t>НК2х10-2,8-03</t>
+        </is>
+      </c>
+      <c r="C1398" s="12" t="inlineStr">
+        <is>
+          <t>Набор клемм НК2 серии 2,8мм, вариант 03(8891+8892, 2 вида по 10шт, в контейнере)</t>
+        </is>
+      </c>
+      <c r="D1398" s="11" t="n"/>
+      <c r="E1398" s="12" t="inlineStr">
+        <is>
+          <t>2601-10, 4323-10, 5991-1</t>
+        </is>
+      </c>
+      <c r="F1398" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ae69.ru/files/_docs/3520546.png,https://www.ae69.ru/files/_docs/6807376.png</t>
+        </is>
+      </c>
+      <c r="G1398" s="11" t="inlineStr">
+        <is>
+          <t>f10</t>
+        </is>
+      </c>
     </row>
     <row r="1399" ht="18" customHeight="1">
-      <c r="A1399" s="15" t="n"/>
-      <c r="B1399" s="15" t="n"/>
-      <c r="C1399" s="15" t="n"/>
-      <c r="D1399" s="15" t="n"/>
-      <c r="E1399" s="15" t="n"/>
-      <c r="F1399" s="15" t="n"/>
-      <c r="G1399" s="15" t="n"/>
+      <c r="A1399" s="11" t="inlineStr">
+        <is>
+          <t>6408</t>
+        </is>
+      </c>
+      <c r="B1399" s="11" t="inlineStr">
+        <is>
+          <t>НК2х10-4,8-01</t>
+        </is>
+      </c>
+      <c r="C1399" s="12" t="inlineStr">
+        <is>
+          <t>Набор клемм НК2 серии 4,8мм, вариант 01(8071+8073, 2 вида по 10шт, в контейнере)</t>
+        </is>
+      </c>
+      <c r="D1399" s="11" t="n"/>
+      <c r="E1399" s="12" t="inlineStr">
+        <is>
+          <t>1483-10, 154-10, 5991-1</t>
+        </is>
+      </c>
+      <c r="F1399" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ae69.ru/files/_docs/6036867.png,https://www.ae69.ru/files/_docs/9343948.png</t>
+        </is>
+      </c>
+      <c r="G1399" s="11" t="inlineStr">
+        <is>
+          <t>f10</t>
+        </is>
+      </c>
     </row>
     <row r="1400" ht="18" customHeight="1">
-      <c r="A1400" s="15" t="n"/>
-      <c r="B1400" s="15" t="n"/>
-      <c r="C1400" s="15" t="n"/>
-      <c r="D1400" s="15" t="n"/>
-      <c r="E1400" s="15" t="n"/>
-      <c r="F1400" s="15" t="n"/>
-      <c r="G1400" s="15" t="n"/>
+      <c r="A1400" s="11" t="inlineStr">
+        <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="B1400" s="11" t="inlineStr">
+        <is>
+          <t>НК2х10-6,3-01</t>
+        </is>
+      </c>
+      <c r="C1400" s="12" t="inlineStr">
+        <is>
+          <t>Набор клемм НК2 серии 6,3мм, вариант 01(8008/1+8004/1, 2 вида по 10шт, в контейнере)</t>
+        </is>
+      </c>
+      <c r="D1400" s="11" t="n"/>
+      <c r="E1400" s="12" t="inlineStr">
+        <is>
+          <t>2626-10, 2602-10, 5991-1</t>
+        </is>
+      </c>
+      <c r="F1400" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ae69.ru/files/_docs/9121003.jpg,https://www.ae69.ru/files/_docs/3342661.jpg</t>
+        </is>
+      </c>
+      <c r="G1400" s="11" t="inlineStr">
+        <is>
+          <t>f10</t>
+        </is>
+      </c>
     </row>
     <row r="1401" ht="18" customHeight="1">
-      <c r="A1401" s="15" t="n"/>
-      <c r="B1401" s="15" t="n"/>
-      <c r="C1401" s="15" t="n"/>
-      <c r="D1401" s="15" t="n"/>
-      <c r="E1401" s="15" t="n"/>
-      <c r="F1401" s="15" t="n"/>
-      <c r="G1401" s="15" t="n"/>
+      <c r="A1401" s="11" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="B1401" s="11" t="inlineStr">
+        <is>
+          <t>НК2х10-6,3-02</t>
+        </is>
+      </c>
+      <c r="C1401" s="12" t="inlineStr">
+        <is>
+          <t>Набор клемм НК2 серии 6,3мм, вариант 02(8008/1+8008/2, 2 вида по 10шт, в контейнере)</t>
+        </is>
+      </c>
+      <c r="D1401" s="11" t="n"/>
+      <c r="E1401" s="12" t="inlineStr">
+        <is>
+          <t>2626-10, 2600-10, 5991-1</t>
+        </is>
+      </c>
+      <c r="F1401" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ae69.ru/files/_docs/2008784.png,https://www.ae69.ru/files/_docs/4471914.png</t>
+        </is>
+      </c>
+      <c r="G1401" s="11" t="inlineStr">
+        <is>
+          <t>f10</t>
+        </is>
+      </c>
     </row>
     <row r="1402" ht="18" customHeight="1">
-      <c r="A1402" s="15" t="n"/>
-      <c r="B1402" s="15" t="n"/>
-      <c r="C1402" s="15" t="n"/>
-      <c r="D1402" s="15" t="n"/>
-      <c r="E1402" s="15" t="n"/>
-      <c r="F1402" s="15" t="n"/>
-      <c r="G1402" s="15" t="n"/>
+      <c r="A1402" s="11" t="inlineStr">
+        <is>
+          <t>2617</t>
+        </is>
+      </c>
+      <c r="B1402" s="11" t="inlineStr">
+        <is>
+          <t>НК2х10-6,3-03</t>
+        </is>
+      </c>
+      <c r="C1402" s="12" t="inlineStr">
+        <is>
+          <t>Набор клемм НК2 серии 6,3мм, вариант 03(8004/1+8004/2, 2 вида по 10шт, в контейнере)</t>
+        </is>
+      </c>
+      <c r="D1402" s="11" t="n"/>
+      <c r="E1402" s="12" t="inlineStr">
+        <is>
+          <t>2602-10, 3151-10, 5991-1</t>
+        </is>
+      </c>
+      <c r="F1402" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ae69.ru/files/_docs/3079437.png,https://www.ae69.ru/files/_docs/4337057.png</t>
+        </is>
+      </c>
+      <c r="G1402" s="11" t="inlineStr">
+        <is>
+          <t>f10</t>
+        </is>
+      </c>
     </row>
     <row r="1403" ht="18" customHeight="1">
-      <c r="A1403" s="15" t="n"/>
-      <c r="B1403" s="15" t="n"/>
-      <c r="C1403" s="15" t="n"/>
-      <c r="D1403" s="15" t="n"/>
-      <c r="E1403" s="15" t="n"/>
-      <c r="F1403" s="15" t="n"/>
-      <c r="G1403" s="15" t="n"/>
+      <c r="A1403" s="11" t="inlineStr">
+        <is>
+          <t>2237</t>
+        </is>
+      </c>
+      <c r="B1403" s="11" t="inlineStr">
+        <is>
+          <t>НК2х10-6,3-04</t>
+        </is>
+      </c>
+      <c r="C1403" s="12" t="inlineStr">
+        <is>
+          <t>Набор клемм НК2 серии 6,3мм, вариант 04(8006/1+8006/2, 2 вида по 10шт, в контейнере)</t>
+        </is>
+      </c>
+      <c r="D1403" s="11" t="n"/>
+      <c r="E1403" s="12" t="inlineStr">
+        <is>
+          <t>2890-10, 5093-10, 5991-1</t>
+        </is>
+      </c>
+      <c r="F1403" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ae69.ru/files/_docs/6246213.png,https://www.ae69.ru/files/_docs/8875010.png</t>
+        </is>
+      </c>
+      <c r="G1403" s="11" t="inlineStr">
+        <is>
+          <t>f10</t>
+        </is>
+      </c>
     </row>
     <row r="1404" ht="18" customHeight="1">
-      <c r="A1404" s="15" t="n"/>
-      <c r="B1404" s="15" t="n"/>
-      <c r="C1404" s="15" t="n"/>
-      <c r="D1404" s="15" t="n"/>
-      <c r="E1404" s="15" t="n"/>
-      <c r="F1404" s="15" t="n"/>
-      <c r="G1404" s="15" t="n"/>
+      <c r="A1404" s="11" t="inlineStr">
+        <is>
+          <t>779</t>
+        </is>
+      </c>
+      <c r="B1404" s="11" t="inlineStr">
+        <is>
+          <t>НК2х10-Б-01</t>
+        </is>
+      </c>
+      <c r="C1404" s="12" t="inlineStr">
+        <is>
+          <t>Набор клемм НК2 "под болт", вариант 01(8526+8535, 2 вида по 10шт, в контейнере)</t>
+        </is>
+      </c>
+      <c r="D1404" s="11" t="n"/>
+      <c r="E1404" s="12" t="inlineStr">
+        <is>
+          <t>2603-10, 8337-10, 5991-1</t>
+        </is>
+      </c>
+      <c r="F1404" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ae69.ru/files/_docs/1920438.png,https://www.ae69.ru/files/_docs/8489368.png</t>
+        </is>
+      </c>
+      <c r="G1404" s="11" t="inlineStr">
+        <is>
+          <t>f10</t>
+        </is>
+      </c>
     </row>
     <row r="1405" ht="18" customHeight="1">
-      <c r="A1405" s="15" t="n"/>
-      <c r="B1405" s="15" t="n"/>
-      <c r="C1405" s="15" t="n"/>
-      <c r="D1405" s="15" t="n"/>
-      <c r="E1405" s="15" t="n"/>
-      <c r="F1405" s="15" t="n"/>
-      <c r="G1405" s="15" t="n"/>
+      <c r="A1405" s="11" t="inlineStr">
+        <is>
+          <t>2570</t>
+        </is>
+      </c>
+      <c r="B1405" s="11" t="inlineStr">
+        <is>
+          <t>НК2х10-Б-02</t>
+        </is>
+      </c>
+      <c r="C1405" s="12" t="inlineStr">
+        <is>
+          <t>Набор клемм НК2 "под болт", вариант 02(8528+8537, 2 вида по 10шт, в контейнере)</t>
+        </is>
+      </c>
+      <c r="D1405" s="11" t="n"/>
+      <c r="E1405" s="12" t="inlineStr">
+        <is>
+          <t>2604-10, 3329-10, 5991-1</t>
+        </is>
+      </c>
+      <c r="F1405" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ae69.ru/files/_docs/8397077.png,https://www.ae69.ru/files/_docs/4811308.png</t>
+        </is>
+      </c>
+      <c r="G1405" s="11" t="inlineStr">
+        <is>
+          <t>f10</t>
+        </is>
+      </c>
     </row>
     <row r="1406" ht="18" customHeight="1">
-      <c r="A1406" s="15" t="n"/>
-      <c r="B1406" s="15" t="n"/>
-      <c r="C1406" s="15" t="n"/>
-      <c r="D1406" s="15" t="n"/>
-      <c r="E1406" s="15" t="n"/>
-      <c r="F1406" s="15" t="n"/>
-      <c r="G1406" s="15" t="n"/>
+      <c r="A1406" s="11" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="B1406" s="11" t="inlineStr">
+        <is>
+          <t>НК2х10-Кр-01</t>
+        </is>
+      </c>
+      <c r="C1406" s="12" t="inlineStr">
+        <is>
+          <t>Набор клемм НК2 круглые, вариант 01(DJ221-4A+DJ211-4A, 2 вида по 10шт, в контейнере)</t>
+        </is>
+      </c>
+      <c r="D1406" s="11" t="n"/>
+      <c r="E1406" s="12" t="inlineStr">
+        <is>
+          <t>4931-10, 4932-10, 5991-1</t>
+        </is>
+      </c>
+      <c r="F1406" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ae69.ru/files/_docs/5858340.png,https://www.ae69.ru/files/_docs/2541922.png</t>
+        </is>
+      </c>
+      <c r="G1406" s="11" t="inlineStr">
+        <is>
+          <t>f10</t>
+        </is>
+      </c>
     </row>
     <row r="1407" ht="18" customHeight="1">
-      <c r="A1407" s="15" t="n"/>
-      <c r="B1407" s="15" t="n"/>
-      <c r="C1407" s="15" t="n"/>
-      <c r="D1407" s="15" t="n"/>
-      <c r="E1407" s="15" t="n"/>
-      <c r="F1407" s="15" t="n"/>
-      <c r="G1407" s="15" t="n"/>
+      <c r="A1407" s="11" t="inlineStr">
+        <is>
+          <t>2324</t>
+        </is>
+      </c>
+      <c r="B1407" s="11" t="inlineStr">
+        <is>
+          <t>НК2х10-Л-01</t>
+        </is>
+      </c>
+      <c r="C1407" s="12" t="inlineStr">
+        <is>
+          <t>Набор клемм НК2 "лира", вариант 01(серии 2,8+4,8мм, 2 вида по 10шт, в контейнере)</t>
+        </is>
+      </c>
+      <c r="D1407" s="11" t="n"/>
+      <c r="E1407" s="12" t="inlineStr">
+        <is>
+          <t>3124-10, 7174-10, 5991-1</t>
+        </is>
+      </c>
+      <c r="F1407" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ae69.ru/files/_docs/8492638.png,https://www.ae69.ru/files/_docs/5509150.png</t>
+        </is>
+      </c>
+      <c r="G1407" s="11" t="inlineStr">
+        <is>
+          <t>f10</t>
+        </is>
+      </c>
     </row>
     <row r="1408" ht="18" customHeight="1">
-      <c r="A1408" s="15" t="n"/>
-      <c r="B1408" s="15" t="n"/>
-      <c r="C1408" s="15" t="n"/>
-      <c r="D1408" s="15" t="n"/>
-      <c r="E1408" s="15" t="n"/>
-      <c r="F1408" s="15" t="n"/>
-      <c r="G1408" s="15" t="n"/>
+      <c r="A1408" s="11" t="inlineStr">
+        <is>
+          <t>5603</t>
+        </is>
+      </c>
+      <c r="B1408" s="11" t="inlineStr">
+        <is>
+          <t>НА-01</t>
+        </is>
+      </c>
+      <c r="C1408" s="12" t="inlineStr">
+        <is>
+          <t>Набор автоэлектрика НА-01(с изолентой, блистер)</t>
+        </is>
+      </c>
+      <c r="D1408" s="11" t="n"/>
+      <c r="E1408" s="12" t="inlineStr">
+        <is>
+          <t>7396-1, 8823-1, 3733-2, 3734-2, 1342-2, 5647-2, 1485-1</t>
+        </is>
+      </c>
+      <c r="F1408" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ae69.ru/files/_docs/4929628.jpg,https://www.ae69.ru/files/_docs/1902223.jpg,https://www.ae69.ru/files/_docs/6666811.jpg</t>
+        </is>
+      </c>
+      <c r="G1408" s="11" t="n"/>
     </row>
     <row r="1409" ht="18" customHeight="1">
-      <c r="A1409" s="15" t="n"/>
-      <c r="B1409" s="15" t="n"/>
-      <c r="C1409" s="15" t="n"/>
-      <c r="D1409" s="15" t="n"/>
-      <c r="E1409" s="15" t="n"/>
-      <c r="F1409" s="15" t="n"/>
-      <c r="G1409" s="15" t="n"/>
+      <c r="A1409" s="11" t="inlineStr">
+        <is>
+          <t>5754</t>
+        </is>
+      </c>
+      <c r="B1409" s="11" t="inlineStr">
+        <is>
+          <t>НА-02</t>
+        </is>
+      </c>
+      <c r="C1409" s="12" t="inlineStr">
+        <is>
+          <t>Набор автоэлектрика НА-02(без изоленты, блистер)</t>
+        </is>
+      </c>
+      <c r="D1409" s="11" t="n"/>
+      <c r="E1409" s="12" t="inlineStr">
+        <is>
+          <t>7396-1, 3733-2, 3734-2, 1342-2, 5647-2, 1485-1</t>
+        </is>
+      </c>
+      <c r="F1409" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ae69.ru/files/_docs/9278278.jpg,https://www.ae69.ru/files/_docs/9531127.jpg,https://www.ae69.ru/files/_docs/8166717.jpg</t>
+        </is>
+      </c>
+      <c r="G1409" s="11" t="n"/>
     </row>
     <row r="1410" ht="18" customHeight="1">
       <c r="A1410" s="15" t="n"/>
@@ -42189,10 +42581,163 @@
       <c r="F1422" s="15" t="n"/>
       <c r="G1422" s="15" t="n"/>
     </row>
+    <row r="1423" ht="18" customHeight="1">
+      <c r="A1423" s="15" t="n"/>
+      <c r="B1423" s="15" t="n"/>
+      <c r="C1423" s="15" t="n"/>
+      <c r="D1423" s="15" t="n"/>
+      <c r="E1423" s="15" t="n"/>
+      <c r="F1423" s="15" t="n"/>
+      <c r="G1423" s="15" t="n"/>
+    </row>
+    <row r="1424" ht="18" customHeight="1">
+      <c r="A1424" s="15" t="n"/>
+      <c r="B1424" s="15" t="n"/>
+      <c r="C1424" s="15" t="n"/>
+      <c r="D1424" s="15" t="n"/>
+      <c r="E1424" s="15" t="n"/>
+      <c r="F1424" s="15" t="n"/>
+      <c r="G1424" s="15" t="n"/>
+    </row>
+    <row r="1425" ht="18" customHeight="1">
+      <c r="A1425" s="15" t="n"/>
+      <c r="B1425" s="15" t="n"/>
+      <c r="C1425" s="15" t="n"/>
+      <c r="D1425" s="15" t="n"/>
+      <c r="E1425" s="15" t="n"/>
+      <c r="F1425" s="15" t="n"/>
+      <c r="G1425" s="15" t="n"/>
+    </row>
+    <row r="1426" ht="18" customHeight="1">
+      <c r="A1426" s="15" t="n"/>
+      <c r="B1426" s="15" t="n"/>
+      <c r="C1426" s="15" t="n"/>
+      <c r="D1426" s="15" t="n"/>
+      <c r="E1426" s="15" t="n"/>
+      <c r="F1426" s="15" t="n"/>
+      <c r="G1426" s="15" t="n"/>
+    </row>
+    <row r="1427" ht="18" customHeight="1">
+      <c r="A1427" s="15" t="n"/>
+      <c r="B1427" s="15" t="n"/>
+      <c r="C1427" s="15" t="n"/>
+      <c r="D1427" s="15" t="n"/>
+      <c r="E1427" s="15" t="n"/>
+      <c r="F1427" s="15" t="n"/>
+      <c r="G1427" s="15" t="n"/>
+    </row>
+    <row r="1428" ht="18" customHeight="1">
+      <c r="A1428" s="15" t="n"/>
+      <c r="B1428" s="15" t="n"/>
+      <c r="C1428" s="15" t="n"/>
+      <c r="D1428" s="15" t="n"/>
+      <c r="E1428" s="15" t="n"/>
+      <c r="F1428" s="15" t="n"/>
+      <c r="G1428" s="15" t="n"/>
+    </row>
+    <row r="1429" ht="18" customHeight="1">
+      <c r="A1429" s="15" t="n"/>
+      <c r="B1429" s="15" t="n"/>
+      <c r="C1429" s="15" t="n"/>
+      <c r="D1429" s="15" t="n"/>
+      <c r="E1429" s="15" t="n"/>
+      <c r="F1429" s="15" t="n"/>
+      <c r="G1429" s="15" t="n"/>
+    </row>
+    <row r="1430" ht="18" customHeight="1">
+      <c r="A1430" s="15" t="n"/>
+      <c r="B1430" s="15" t="n"/>
+      <c r="C1430" s="15" t="n"/>
+      <c r="D1430" s="15" t="n"/>
+      <c r="E1430" s="15" t="n"/>
+      <c r="F1430" s="15" t="n"/>
+      <c r="G1430" s="15" t="n"/>
+    </row>
+    <row r="1431" ht="18" customHeight="1">
+      <c r="A1431" s="15" t="n"/>
+      <c r="B1431" s="15" t="n"/>
+      <c r="C1431" s="15" t="n"/>
+      <c r="D1431" s="15" t="n"/>
+      <c r="E1431" s="15" t="n"/>
+      <c r="F1431" s="15" t="n"/>
+      <c r="G1431" s="15" t="n"/>
+    </row>
+    <row r="1432" ht="18" customHeight="1">
+      <c r="A1432" s="15" t="n"/>
+      <c r="B1432" s="15" t="n"/>
+      <c r="C1432" s="15" t="n"/>
+      <c r="D1432" s="15" t="n"/>
+      <c r="E1432" s="15" t="n"/>
+      <c r="F1432" s="15" t="n"/>
+      <c r="G1432" s="15" t="n"/>
+    </row>
+    <row r="1433" ht="18" customHeight="1">
+      <c r="A1433" s="15" t="n"/>
+      <c r="B1433" s="15" t="n"/>
+      <c r="C1433" s="15" t="n"/>
+      <c r="D1433" s="15" t="n"/>
+      <c r="E1433" s="15" t="n"/>
+      <c r="F1433" s="15" t="n"/>
+      <c r="G1433" s="15" t="n"/>
+    </row>
+    <row r="1434" ht="18" customHeight="1">
+      <c r="A1434" s="15" t="n"/>
+      <c r="B1434" s="15" t="n"/>
+      <c r="C1434" s="15" t="n"/>
+      <c r="D1434" s="15" t="n"/>
+      <c r="E1434" s="15" t="n"/>
+      <c r="F1434" s="15" t="n"/>
+      <c r="G1434" s="15" t="n"/>
+    </row>
+    <row r="1435" ht="18" customHeight="1">
+      <c r="A1435" s="15" t="n"/>
+      <c r="B1435" s="15" t="n"/>
+      <c r="C1435" s="15" t="n"/>
+      <c r="D1435" s="15" t="n"/>
+      <c r="E1435" s="15" t="n"/>
+      <c r="F1435" s="15" t="n"/>
+      <c r="G1435" s="15" t="n"/>
+    </row>
+    <row r="1436" ht="18" customHeight="1">
+      <c r="A1436" s="15" t="n"/>
+      <c r="B1436" s="15" t="n"/>
+      <c r="C1436" s="15" t="n"/>
+      <c r="D1436" s="15" t="n"/>
+      <c r="E1436" s="15" t="n"/>
+      <c r="F1436" s="15" t="n"/>
+      <c r="G1436" s="15" t="n"/>
+    </row>
+    <row r="1437" ht="18" customHeight="1">
+      <c r="A1437" s="15" t="n"/>
+      <c r="B1437" s="15" t="n"/>
+      <c r="C1437" s="15" t="n"/>
+      <c r="D1437" s="15" t="n"/>
+      <c r="E1437" s="15" t="n"/>
+      <c r="F1437" s="15" t="n"/>
+      <c r="G1437" s="15" t="n"/>
+    </row>
+    <row r="1438" ht="18" customHeight="1">
+      <c r="A1438" s="15" t="n"/>
+      <c r="B1438" s="15" t="n"/>
+      <c r="C1438" s="15" t="n"/>
+      <c r="D1438" s="15" t="n"/>
+      <c r="E1438" s="15" t="n"/>
+      <c r="F1438" s="15" t="n"/>
+      <c r="G1438" s="15" t="n"/>
+    </row>
+    <row r="1439" ht="18" customHeight="1">
+      <c r="A1439" s="15" t="n"/>
+      <c r="B1439" s="15" t="n"/>
+      <c r="C1439" s="15" t="n"/>
+      <c r="D1439" s="15" t="n"/>
+      <c r="E1439" s="15" t="n"/>
+      <c r="F1439" s="15" t="n"/>
+      <c r="G1439" s="15" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1392"/>
+  <autoFilter ref="A1:G1409"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G1422" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Категория" error="Выберите код со листа «Категории»" promptTitle="Категория" prompt="Код категории со листа «Категории»" type="list">
+    <dataValidation sqref="G2:G1439" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Категория" error="Выберите код со листа «Категории»" promptTitle="Категория" prompt="Код категории со листа «Категории»" type="list">
       <formula1>Категории!$A$2:$A$60</formula1>
     </dataValidation>
   </dataValidations>
@@ -42244,7 +42789,7 @@
         </is>
       </c>
       <c r="C2" s="18" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3">
@@ -42904,7 +43449,7 @@
         </is>
       </c>
       <c r="C46" s="18" t="n">
-        <v>108</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47">
@@ -42960,7 +43505,7 @@
         </is>
       </c>
       <c r="C50" s="18" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -42976,7 +43521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E752"/>
+  <dimension ref="A1:E754"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -60090,8 +60635,54 @@
       </c>
       <c r="E752" s="13" t="n"/>
     </row>
+    <row r="753">
+      <c r="A753" s="11" t="inlineStr">
+        <is>
+          <t>3733</t>
+        </is>
+      </c>
+      <c r="B753" s="11" t="inlineStr">
+        <is>
+          <t>VBS 1(ГСИ 1.5)</t>
+        </is>
+      </c>
+      <c r="C753" s="12" t="inlineStr">
+        <is>
+          <t>Клемма "трубка" соединит. с полн.изоляц.ПВХ(под пр.от 0,50 до 1,50мм кв лужён., красная) мин.100шт</t>
+        </is>
+      </c>
+      <c r="D753" s="11" t="inlineStr">
+        <is>
+          <t>Клеммы</t>
+        </is>
+      </c>
+      <c r="E753" s="13" t="n"/>
+    </row>
+    <row r="754">
+      <c r="A754" s="11" t="inlineStr">
+        <is>
+          <t>3734</t>
+        </is>
+      </c>
+      <c r="B754" s="11" t="inlineStr">
+        <is>
+          <t>VBS 2(ГСИ 2,5)</t>
+        </is>
+      </c>
+      <c r="C754" s="12" t="inlineStr">
+        <is>
+          <t>Клемма "трубка" соединит. с полн.изоляц.ПВХ(под пр.от 1,50 до 2,50мм кв лужён., синяя) мин.100шт</t>
+        </is>
+      </c>
+      <c r="D754" s="11" t="inlineStr">
+        <is>
+          <t>Клеммы</t>
+        </is>
+      </c>
+      <c r="E754" s="13" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E752"/>
+  <autoFilter ref="A1:E754"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/AE69-base.xlsx
+++ b/AE69-base.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справка" sheetId="1" r:id="Rc4d0debf339a4e59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" r:id="R4be4754dc14f43c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Категории" sheetId="3" r:id="R4cd3ac9632d34177"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Без комплектующих" sheetId="4" r:id="R47373c5b90014346"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Без фото" sheetId="5" r:id="R917fde9d3b494f3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справка" sheetId="1" r:id="R22bbca6532d74d0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" r:id="Re69f6374c3754f16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Категории" sheetId="3" r:id="R16809d25b8304d4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Без комплектующих" sheetId="4" r:id="R5b8507743b8c40c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Без фото" sheetId="5" r:id="Rf356e7644ec9496e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -545,7 +545,7 @@
         </x:is>
       </x:c>
       <x:c r="B4" s="4" t="str">
-        <x:v>каталог 22 · 15.10.2026 · 1416 позиций</x:v>
+        <x:v>каталог 23 · 16.10.2026 · 1416 позиций</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -10723,10 +10723,8 @@
         </x:is>
       </x:c>
       <x:c r="D329" s="11" t="n"/>
-      <x:c r="E329" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">3151-1, 539-120</x:t>
-        </x:is>
+      <x:c r="E329" s="12" t="str">
+        <x:v>3151-1, 539-0.24</x:v>
       </x:c>
       <x:c r="F329" s="12" t="inlineStr">
         <x:is>

--- a/AE69-base.xlsx
+++ b/AE69-base.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справка" sheetId="1" r:id="R22bbca6532d74d0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" r:id="Re69f6374c3754f16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Категории" sheetId="3" r:id="R16809d25b8304d4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Без комплектующих" sheetId="4" r:id="R5b8507743b8c40c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Без фото" sheetId="5" r:id="Rf356e7644ec9496e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справка" sheetId="1" r:id="Reb3e3706f9c04d13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" r:id="R53ea1d0df18844fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Категории" sheetId="3" r:id="R2dd98d53904745e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Без комплектующих" sheetId="4" r:id="Rfdbfbdf5d4454514"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Без фото" sheetId="5" r:id="Ra1d10d76eab847f4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -545,7 +545,7 @@
         </x:is>
       </x:c>
       <x:c r="B4" s="4" t="str">
-        <x:v>каталог 23 · 16.10.2026 · 1416 позиций</x:v>
+        <x:v>каталог 24 · 16.10.2026 · 1420 позиций</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -555,7 +555,7 @@
         </x:is>
       </x:c>
       <x:c r="B5" s="4" t="n">
-        <x:v>1056</x:v>
+        <x:v>1058</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -565,7 +565,7 @@
         </x:is>
       </x:c>
       <x:c r="B6" s="4" t="str">
-        <x:v>360  (оранжевые ячейки в столбце «Ссылка на фото»)</x:v>
+        <x:v>362  (оранжевые ячейки в столбце «Ссылка на фото»)</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -575,7 +575,7 @@
         </x:is>
       </x:c>
       <x:c r="B7" s="4" t="n">
-        <x:v>660</x:v>
+        <x:v>662</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -585,7 +585,7 @@
         </x:is>
       </x:c>
       <x:c r="B8" s="4" t="str">
-        <x:v>756  (жёлтые ячейки в столбце «Комплектующие»)</x:v>
+        <x:v>758  (жёлтые ячейки в столбце «Комплектующие»)</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -42529,14 +42529,14 @@
         <x:v>80.3710СБК</x:v>
       </x:c>
       <x:c r="C1416" s="12" t="str">
-        <x:v>Выключатель конц. "Приора", "Калина","Гранта","Шеви-Нива" (капота, двери в сборе с проводом и колод.)</x:v>
+        <x:v>Выключатель конц. "Приора", "Калина","Гранта","Шеви-Нива"(капота, двери в сборе с проводом и колод.)</x:v>
       </x:c>
       <x:c r="D1416" s="11"/>
       <x:c r="E1416" s="12" t="str">
-        <x:v>3752-1, 6940-2, 5844-240</x:v>
+        <x:v>3752-1, 6940-2, 6925-1, 5844-240</x:v>
       </x:c>
       <x:c r="F1416" s="12" t="str">
-        <x:v>https://www.ae69.ru/files/_docs/1889497.jpg</x:v>
+        <x:v>https://www.ae69.ru/files/_docs/3532531.jpg</x:v>
       </x:c>
       <x:c r="G1416" s="11" t="str">
         <x:v>bwt2</x:v>
@@ -42550,54 +42550,86 @@
         <x:v>80.3710СБКП</x:v>
       </x:c>
       <x:c r="C1417" s="12" t="str">
-        <x:v>Выключатель конц. "Приора", "Калина","Гранта","Шеви-Нива" (капота, двери в сб. с пров., кол., пыльн.)</x:v>
+        <x:v>Выключатель конц. "Приора", "Калина","Гранта","Шеви-Нива"(капота, двери в сб. с пров., кол., пыльн.)</x:v>
       </x:c>
       <x:c r="D1417" s="11"/>
       <x:c r="E1417" s="12" t="str">
-        <x:v>3752-1, 6940-2, 5844-240, 397-1</x:v>
+        <x:v>3752-1, 6940-2, 6925-1, 5844-240, 397-1</x:v>
       </x:c>
       <x:c r="F1417" s="12" t="str">
-        <x:v>https://www.ae69.ru/files/_docs/3633336.jpg</x:v>
+        <x:v>https://www.ae69.ru/files/_docs/4303472.jpg</x:v>
       </x:c>
       <x:c r="G1417" s="11" t="str">
         <x:v>bwt2</x:v>
       </x:c>
     </x:row>
     <x:row r="1418" ht="18" customHeight="1">
-      <x:c r="A1418" s="15" t="n"/>
-      <x:c r="B1418" s="15" t="n"/>
-      <x:c r="C1418" s="15" t="n"/>
-      <x:c r="D1418" s="15" t="n"/>
-      <x:c r="E1418" s="15" t="n"/>
-      <x:c r="F1418" s="15" t="n"/>
-      <x:c r="G1418" s="15" t="n"/>
+      <x:c r="A1418" s="11" t="str">
+        <x:v>6986</x:v>
+      </x:c>
+      <x:c r="B1418" s="11" t="str">
+        <x:v>79.3710</x:v>
+      </x:c>
+      <x:c r="C1418" s="12" t="str">
+        <x:v>Выключатель конц. "Приора", "Калина", "Гранта", "Шеви-Нива" (на дверь) "Авар" Псков</x:v>
+      </x:c>
+      <x:c r="D1418" s="11"/>
+      <x:c r="E1418" s="13"/>
+      <x:c r="F1418" s="14"/>
+      <x:c r="G1418" s="11"/>
     </x:row>
     <x:row r="1419" ht="18" customHeight="1">
-      <x:c r="A1419" s="15" t="n"/>
-      <x:c r="B1419" s="15" t="n"/>
-      <x:c r="C1419" s="15" t="n"/>
-      <x:c r="D1419" s="15" t="n"/>
-      <x:c r="E1419" s="15" t="n"/>
-      <x:c r="F1419" s="15" t="n"/>
-      <x:c r="G1419" s="15" t="n"/>
+      <x:c r="A1419" s="11" t="str">
+        <x:v>8007</x:v>
+      </x:c>
+      <x:c r="B1419" s="11" t="str">
+        <x:v>78.3710.000</x:v>
+      </x:c>
+      <x:c r="C1419" s="12" t="str">
+        <x:v>Выключатель конц. УАЗ Патриот (на капот, дверь) "Авар" Псков</x:v>
+      </x:c>
+      <x:c r="D1419" s="11"/>
+      <x:c r="E1419" s="13"/>
+      <x:c r="F1419" s="14"/>
+      <x:c r="G1419" s="11"/>
     </x:row>
     <x:row r="1420" ht="18" customHeight="1">
-      <x:c r="A1420" s="15" t="n"/>
-      <x:c r="B1420" s="15" t="n"/>
-      <x:c r="C1420" s="15" t="n"/>
-      <x:c r="D1420" s="15" t="n"/>
-      <x:c r="E1420" s="15" t="n"/>
-      <x:c r="F1420" s="15" t="n"/>
-      <x:c r="G1420" s="15" t="n"/>
+      <x:c r="A1420" s="11" t="str">
+        <x:v>7821</x:v>
+      </x:c>
+      <x:c r="B1420" s="11" t="str">
+        <x:v>79.3710СБК</x:v>
+      </x:c>
+      <x:c r="C1420" s="12" t="str">
+        <x:v>Выключатель конц. "Приора", "Калина","Гранта","Шеви-Нива"(на дверь, в сборе с проводом и колодкой)</x:v>
+      </x:c>
+      <x:c r="D1420" s="11"/>
+      <x:c r="E1420" s="12" t="str">
+        <x:v>6986-1, 2599-2, 7823-1, 1461-240</x:v>
+      </x:c>
+      <x:c r="F1420" s="12" t="str">
+        <x:v>https://www.ae69.ru/files/_docs/1700919.jpg</x:v>
+      </x:c>
+      <x:c r="G1420" s="11"/>
     </x:row>
     <x:row r="1421" ht="18" customHeight="1">
-      <x:c r="A1421" s="15" t="n"/>
-      <x:c r="B1421" s="15" t="n"/>
-      <x:c r="C1421" s="15" t="n"/>
-      <x:c r="D1421" s="15" t="n"/>
-      <x:c r="E1421" s="15" t="n"/>
-      <x:c r="F1421" s="15" t="n"/>
-      <x:c r="G1421" s="15" t="n"/>
+      <x:c r="A1421" s="11" t="str">
+        <x:v>8009</x:v>
+      </x:c>
+      <x:c r="B1421" s="11" t="str">
+        <x:v>78.3710СБ</x:v>
+      </x:c>
+      <x:c r="C1421" s="12" t="str">
+        <x:v>Выключатель конц. УАЗ Патриот(на капот, дверь в сборе с проводом и клеммами)</x:v>
+      </x:c>
+      <x:c r="D1421" s="11"/>
+      <x:c r="E1421" s="12" t="str">
+        <x:v>8007-1, 2890-2, 539-240, 6619-2</x:v>
+      </x:c>
+      <x:c r="F1421" s="12" t="str">
+        <x:v>https://www.ae69.ru/files/_docs/1700919.jpg</x:v>
+      </x:c>
+      <x:c r="G1421" s="11"/>
     </x:row>
     <x:row r="1422" ht="18" customHeight="1">
       <x:c r="A1422" s="15" t="n"/>
@@ -43528,7 +43560,7 @@
         </x:is>
       </x:c>
       <x:c r="C50" s="18" t="n">
-        <x:v>162</x:v>
+        <x:v>166</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -54817,6 +54849,36 @@
       </x:c>
       <x:c r="E757" s="13"/>
     </x:row>
+    <x:row r="758">
+      <x:c r="A758" s="11" t="str">
+        <x:v>6986</x:v>
+      </x:c>
+      <x:c r="B758" s="11" t="str">
+        <x:v>79.3710</x:v>
+      </x:c>
+      <x:c r="C758" s="12" t="str">
+        <x:v>Выключатель конц. "Приора", "Калина", "Гранта", "Шеви-Нива" (на дверь) "Авар" Псков</x:v>
+      </x:c>
+      <x:c r="D758" s="11" t="str">
+        <x:v>Без категории</x:v>
+      </x:c>
+      <x:c r="E758" s="13"/>
+    </x:row>
+    <x:row r="759">
+      <x:c r="A759" s="11" t="str">
+        <x:v>8007</x:v>
+      </x:c>
+      <x:c r="B759" s="11" t="str">
+        <x:v>78.3710.000</x:v>
+      </x:c>
+      <x:c r="C759" s="12" t="str">
+        <x:v>Выключатель конц. УАЗ Патриот (на капот, дверь) "Авар" Псков</x:v>
+      </x:c>
+      <x:c r="D759" s="11" t="str">
+        <x:v>Без категории</x:v>
+      </x:c>
+      <x:c r="E759" s="13"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -60216,17 +60278,33 @@
       <x:c r="E361" s="14"/>
     </x:row>
     <x:row r="362">
-      <x:c r="A362" s="11"/>
-      <x:c r="B362" s="11"/>
-      <x:c r="C362" s="12"/>
-      <x:c r="D362" s="11"/>
+      <x:c r="A362" s="11" t="str">
+        <x:v>6986</x:v>
+      </x:c>
+      <x:c r="B362" s="11" t="str">
+        <x:v>79.3710</x:v>
+      </x:c>
+      <x:c r="C362" s="12" t="str">
+        <x:v>Выключатель конц. "Приора", "Калина", "Гранта", "Шеви-Нива" (на дверь) "Авар" Псков</x:v>
+      </x:c>
+      <x:c r="D362" s="11" t="str">
+        <x:v>Без категории</x:v>
+      </x:c>
       <x:c r="E362" s="14"/>
     </x:row>
     <x:row r="363">
-      <x:c r="A363" s="11"/>
-      <x:c r="B363" s="11"/>
-      <x:c r="C363" s="12"/>
-      <x:c r="D363" s="11"/>
+      <x:c r="A363" s="11" t="str">
+        <x:v>8007</x:v>
+      </x:c>
+      <x:c r="B363" s="11" t="str">
+        <x:v>78.3710.000</x:v>
+      </x:c>
+      <x:c r="C363" s="12" t="str">
+        <x:v>Выключатель конц. УАЗ Патриот (на капот, дверь) "Авар" Псков</x:v>
+      </x:c>
+      <x:c r="D363" s="11" t="str">
+        <x:v>Без категории</x:v>
+      </x:c>
       <x:c r="E363" s="14"/>
     </x:row>
     <x:row r="364">

--- a/AE69-base.xlsx
+++ b/AE69-base.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справка" sheetId="1" r:id="Reb3e3706f9c04d13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" r:id="R53ea1d0df18844fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Категории" sheetId="3" r:id="R2dd98d53904745e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Без комплектующих" sheetId="4" r:id="Rfdbfbdf5d4454514"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Без фото" sheetId="5" r:id="Ra1d10d76eab847f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справка" sheetId="1" r:id="R1a43b1f49d2e4343"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" r:id="R478f631769484d8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Категории" sheetId="3" r:id="R9fa684f461ed4c60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Без комплектующих" sheetId="4" r:id="R328db057e6664ad5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Без фото" sheetId="5" r:id="Rdc74d3a983ce4314"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -545,7 +545,7 @@
         </x:is>
       </x:c>
       <x:c r="B4" s="4" t="str">
-        <x:v>каталог 24 · 16.10.2026 · 1420 позиций</x:v>
+        <x:v>каталог 25 · 16.10.2026 · 1422 позиции</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -565,7 +565,7 @@
         </x:is>
       </x:c>
       <x:c r="B6" s="4" t="str">
-        <x:v>362  (оранжевые ячейки в столбце «Ссылка на фото»)</x:v>
+        <x:v>364  (оранжевые ячейки в столбце «Ссылка на фото»)</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -575,7 +575,7 @@
         </x:is>
       </x:c>
       <x:c r="B7" s="4" t="n">
-        <x:v>662</x:v>
+        <x:v>663</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -585,7 +585,7 @@
         </x:is>
       </x:c>
       <x:c r="B8" s="4" t="str">
-        <x:v>758  (жёлтые ячейки в столбце «Комплектующие»)</x:v>
+        <x:v>759  (жёлтые ячейки в столбце «Комплектующие»)</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -42632,22 +42632,34 @@
       <x:c r="G1421" s="11"/>
     </x:row>
     <x:row r="1422" ht="18" customHeight="1">
-      <x:c r="A1422" s="15" t="n"/>
-      <x:c r="B1422" s="15" t="n"/>
-      <x:c r="C1422" s="15" t="n"/>
-      <x:c r="D1422" s="15" t="n"/>
-      <x:c r="E1422" s="15" t="n"/>
-      <x:c r="F1422" s="15" t="n"/>
-      <x:c r="G1422" s="15" t="n"/>
+      <x:c r="A1422" s="11" t="str">
+        <x:v>4066</x:v>
+      </x:c>
+      <x:c r="B1422" s="11"/>
+      <x:c r="C1422" s="12" t="str">
+        <x:v>Светодиод Ф5мм(кругл.) (мигающий 2Гц, красный)</x:v>
+      </x:c>
+      <x:c r="D1422" s="11"/>
+      <x:c r="E1422" s="13"/>
+      <x:c r="F1422" s="14"/>
+      <x:c r="G1422" s="11"/>
     </x:row>
     <x:row r="1423" ht="18" customHeight="1">
-      <x:c r="A1423" s="15" t="n"/>
-      <x:c r="B1423" s="15" t="n"/>
-      <x:c r="C1423" s="15" t="n"/>
-      <x:c r="D1423" s="15" t="n"/>
-      <x:c r="E1423" s="15" t="n"/>
-      <x:c r="F1423" s="15" t="n"/>
-      <x:c r="G1423" s="15" t="n"/>
+      <x:c r="A1423" s="11" t="str">
+        <x:v>4496</x:v>
+      </x:c>
+      <x:c r="B1423" s="11" t="str">
+        <x:v>ИС-2к</x:v>
+      </x:c>
+      <x:c r="C1423" s="12" t="str">
+        <x:v>Имитатор сигнализации (красный) 12В</x:v>
+      </x:c>
+      <x:c r="D1423" s="11"/>
+      <x:c r="E1423" s="12" t="str">
+        <x:v>261-1, 3204-2, 4447-0.033, 3686-1, 4724-1, 4066-1, 2897-0.01</x:v>
+      </x:c>
+      <x:c r="F1423" s="12"/>
+      <x:c r="G1423" s="11"/>
     </x:row>
     <x:row r="1424" ht="18" customHeight="1">
       <x:c r="A1424" s="15" t="n"/>
@@ -43560,7 +43572,7 @@
         </x:is>
       </x:c>
       <x:c r="C50" s="18" t="n">
-        <x:v>166</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -54879,6 +54891,19 @@
       </x:c>
       <x:c r="E759" s="13"/>
     </x:row>
+    <x:row r="760">
+      <x:c r="A760" s="11" t="str">
+        <x:v>4066</x:v>
+      </x:c>
+      <x:c r="B760" s="11"/>
+      <x:c r="C760" s="12" t="str">
+        <x:v>Светодиод Ф5мм(кругл.) (мигающий 2Гц, красный)</x:v>
+      </x:c>
+      <x:c r="D760" s="11" t="str">
+        <x:v>Без категории</x:v>
+      </x:c>
+      <x:c r="E760" s="13"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -60308,17 +60333,31 @@
       <x:c r="E363" s="14"/>
     </x:row>
     <x:row r="364">
-      <x:c r="A364" s="11"/>
+      <x:c r="A364" s="11" t="str">
+        <x:v>4066</x:v>
+      </x:c>
       <x:c r="B364" s="11"/>
-      <x:c r="C364" s="12"/>
-      <x:c r="D364" s="11"/>
+      <x:c r="C364" s="12" t="str">
+        <x:v>Светодиод Ф5мм(кругл.) (мигающий 2Гц, красный)</x:v>
+      </x:c>
+      <x:c r="D364" s="11" t="str">
+        <x:v>Без категории</x:v>
+      </x:c>
       <x:c r="E364" s="14"/>
     </x:row>
     <x:row r="365">
-      <x:c r="A365" s="11"/>
-      <x:c r="B365" s="11"/>
-      <x:c r="C365" s="12"/>
-      <x:c r="D365" s="11"/>
+      <x:c r="A365" s="11" t="str">
+        <x:v>4496</x:v>
+      </x:c>
+      <x:c r="B365" s="11" t="str">
+        <x:v>ИС-2к</x:v>
+      </x:c>
+      <x:c r="C365" s="12" t="str">
+        <x:v>Имитатор сигнализации (красный) 12В</x:v>
+      </x:c>
+      <x:c r="D365" s="11" t="str">
+        <x:v>Без категории</x:v>
+      </x:c>
       <x:c r="E365" s="14"/>
     </x:row>
   </x:sheetData>
